--- a/data_execl/base_data/HeroRankupGroup.xlsx
+++ b/data_execl/base_data/HeroRankupGroup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HeroRankupGroup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HeroRankupGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1416,10 +1416,10 @@
         <v>5</v>
       </c>
       <c r="E38" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="0" t="n">
-        <v>0</v>
+        <v>10011</v>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         <v>5</v>
       </c>
       <c r="E39" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="0" t="n">
-        <v>0</v>
+        <v>10012</v>
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         <v>5</v>
       </c>
       <c r="E40" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="0" t="n">
-        <v>0</v>
+        <v>10013</v>
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         <v>5</v>
       </c>
       <c r="E41" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="0" t="n">
-        <v>0</v>
+        <v>10014</v>
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
@@ -1516,10 +1516,10 @@
         <v>5</v>
       </c>
       <c r="E42" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="0" t="n">
-        <v>0</v>
+        <v>10028</v>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         <v>5</v>
       </c>
       <c r="E43" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="0" t="n">
-        <v>0</v>
+        <v>10029</v>
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         <v>5</v>
       </c>
       <c r="E44" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="0" t="n">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>5</v>
       </c>
       <c r="E45" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="0" t="n">
-        <v>0</v>
+        <v>10032</v>
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>5</v>
       </c>
       <c r="E46" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="0" t="n">
-        <v>0</v>
+        <v>10047</v>
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         <v>5</v>
       </c>
       <c r="E47" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="0" t="n">
-        <v>0</v>
+        <v>10048</v>
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>5</v>
       </c>
       <c r="E48" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="0" t="n">
-        <v>0</v>
+        <v>10049</v>
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         <v>5</v>
       </c>
       <c r="E49" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="0" t="n">
-        <v>0</v>
+        <v>10050</v>
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
         <v>5</v>
       </c>
       <c r="E50" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="0" t="n">
-        <v>0</v>
+        <v>10051</v>
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         <v>5</v>
       </c>
       <c r="E51" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="0" t="n">
-        <v>0</v>
+        <v>10067</v>
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         <v>5</v>
       </c>
       <c r="E52" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="0" t="n">
-        <v>0</v>
+        <v>10068</v>
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
         <v>5</v>
       </c>
       <c r="E53" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="0" t="n">
-        <v>0</v>
+        <v>10069</v>
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
         <v>5</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>0</v>
+        <v>10070</v>
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         <v>5</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>0</v>
+        <v>10086</v>
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         <v>5</v>
       </c>
       <c r="E56" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="0" t="n">
-        <v>0</v>
+        <v>10087</v>
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
         <v>5</v>
       </c>
       <c r="E57" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="0" t="n">
-        <v>0</v>
+        <v>10088</v>
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         <v>5</v>
       </c>
       <c r="E58" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="0" t="n">
-        <v>0</v>
+        <v>10089</v>
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
         <v>5</v>
       </c>
       <c r="E59" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="0" t="n">
-        <v>0</v>
+        <v>10031</v>
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
         <v>5</v>
       </c>
       <c r="E60" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="0" t="n">
-        <v>0</v>
+        <v>10015</v>
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
